--- a/output/2026-09-14_18_Croazia_Licko-senjska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-14_18_Croazia_Licko-senjska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-14_18_Croazia_Licko-senjska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-14_18_Croazia_Licko-senjska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Azienda verificata (sito ufficiale, tvrtke.hr, kompass.com). Attivo dal 1990, sede a Kaniža 5 e punto vendita ingrosso a Kralja Zvonimira 14, Gospić, oltre a Lički Osik. Attività principale: materiale edile, con reparto dedicato a 'građevinski alati' (utensili/attrezzi da costruzione) e ferramenta tecnica. Profilo B2B/B2C misto.</t>
+          <t>Azienda verificata (sito ufficiale, tvrtke.hr, kompass.com). Attivo dal 1990, sede a Kaniža 5 e punto vendita ingrosso a Kralja Zvonimira 14, Gospić, oltre a Lički Osik. Attività principale: materiale edile, con reparto dedicato a 'građevinski alati' (utensili/attrezzi da costruzione) e ferramenta tecnica. Profilo B2B/B2C misto. [DUPLICATO — vedi anche: 2026-09-14_03_Croazia_Licko-senjska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Azienda verificata (sito ufficiale, fininfo.hr, companywall.hr). Concessionario/rivenditore autorizzato Husqvarna e STIHL: vendita e assistenza di macchine e utensili motorizzati (motoseghe, decespugliatori, tosaerba, generatori, idropulitrici) per agricoltura, giardinaggio e forestazione. 3 punti vendita + magazzino ingrosso a Lički Osik.</t>
+          <t>Azienda verificata (sito ufficiale, fininfo.hr, companywall.hr). Concessionario/rivenditore autorizzato Husqvarna e STIHL: vendita e assistenza di macchine e utensili motorizzati (motoseghe, decespugliatori, tosaerba, generatori, idropulitrici) per agricoltura, giardinaggio e forestazione. 3 punti vendita + magazzino ingrosso a Lički Osik. [DUPLICATO — vedi anche: 2026-09-14_03_Croazia_Licko-senjska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
